--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -1047,7 +1047,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1377,7 +1377,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2085,7 +2085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2548,7 +2548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2987,7 +2987,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11547,7 +11547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12552,7 +12552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
+          <t>Data status: Sep 2026 locked (data retrieved 2pm, Tue 6 Oct 2026) · Generated 22 Oct 2026, 4:57pm</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12973,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 22 Oct 2026, 4:57pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
